--- a/NACA/assets/compression_TN3781_14.xlsx
+++ b/NACA/assets/compression_TN3781_14.xlsx
@@ -1,45 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eric/Code/misc/buckling_tool/assets/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBF7872-9745-794E-B1B8-CD1870D6AB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="31020" yWindow="6320" windowWidth="18160" windowHeight="17440" firstSheet="1" activeTab="5" xr2:uid="{EBB14005-C621-6B44-88C1-4DF052F65455}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Comp_SSSS" sheetId="1" r:id="rId1"/>
-    <sheet name="Comp_CCCC" sheetId="2" r:id="rId2"/>
-    <sheet name="Comp_SCSC" sheetId="3" r:id="rId3"/>
-    <sheet name="Comp_CSCS" sheetId="4" r:id="rId4"/>
-    <sheet name="Comp_SSSF" sheetId="5" r:id="rId5"/>
-    <sheet name="Comp_CCCS" sheetId="6" r:id="rId6"/>
-    <sheet name="Comp_CSCF" sheetId="7" r:id="rId7"/>
+    <sheet name="Comp_SSSS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Comp_CCCC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comp_SCSC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comp_CSCS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Comp_SSSF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Comp_CCCS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comp_CSCF" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>xData</t>
   </si>
@@ -50,43 +33,60 @@
     <t>reference</t>
   </si>
   <si>
-    <t>NACA-TN-3781, Fig 14</t>
+    <t xml:space="preserve">NACA-TN-3781, Fig 14</t>
   </si>
   <si>
     <t>notes</t>
   </si>
   <si>
-    <t>Curve C. Solid line</t>
+    <t xml:space="preserve">Curve C. Solid line</t>
   </si>
   <si>
-    <t>Curve A. Dashed line</t>
+    <t xml:space="preserve">All edges simply supported</t>
   </si>
   <si>
-    <t>Curve A. Solid line</t>
+    <t xml:space="preserve">Curve A. Dashed line</t>
   </si>
   <si>
-    <t>Curve C. Dashed line.</t>
+    <t xml:space="preserve">All edges clamped</t>
   </si>
   <si>
-    <t>Curve E. Solid line</t>
+    <t xml:space="preserve">Curve A. Solid line</t>
   </si>
   <si>
-    <t>Curve B. Dashed line.</t>
+    <t xml:space="preserve">Loaded edges simply supported, opposite edges clamped</t>
   </si>
   <si>
-    <t>Curve E. Dashed line</t>
+    <t xml:space="preserve">Curve C. Dashed line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loaded edges clamped, opposite edges simply supported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curve E. Solid line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loaded edges simply supported. One opposite edge simply supported, other opposite edge free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curve B. Dashed line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loaded edges clamped. One opposite edge clamped, one simply supported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curve E. Dashed line</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
-      <sz val="12"/>
+      <sz val="12.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -100,18 +100,18 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -129,8 +129,3120 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Comp_SSSS!$A$2:$A$59</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Comp_SSSS!$B$2:$B$59</c:f>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="1001"/>
+        <c:axId val="1002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1002"/>
+        <c:crosses val="autoZero"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="2533649" y="1066799"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Comp_CCCC!$A$2:$A$64</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Comp_CCCC!$B$2:$B$64</c:f>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="664968979"/>
+        <c:axId val="664968980"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="664968979"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="664968980"/>
+        <c:crosses val="autoZero"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="664968980"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="664968979"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="3428999" y="5305424"/>
+      <a:ext cx="4552949" cy="4543424"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Comp_SCSC!$A$2:$A$59</c:f>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Comp_SCSC!$B$2:$B$59</c:f>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="664968981"/>
+        <c:axId val="664968982"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="664968981"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="664968982"/>
+        <c:crosses val="autoZero"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="664968982"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="664968981"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm>
+      <a:off x="3428999" y="6076949"/>
+      <a:ext cx="4552949" cy="2724149"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="463616603" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="2533649" y="1066799"/>
+        <a:ext cx="4552949" cy="2724149"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="384321683" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3428999" y="5305424"/>
+        <a:ext cx="4552949" cy="4543424"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>438149</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1784004359" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3428999" y="6076949"/>
+        <a:ext cx="4552949" cy="2724149"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -172,108 +3284,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -281,7 +3299,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -307,7 +3325,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -384,7 +3402,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -415,21 +3433,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A8E2DE-CFF0-8943-AC71-ED87037327F6}">
-  <dimension ref="A1:E59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +3448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
         <v>0.39677547537429297</v>
       </c>
@@ -451,7 +3462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
         <v>0.40178487918720401</v>
       </c>
@@ -465,15 +3476,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4">
         <v>0.41396516233742597</v>
       </c>
       <c r="B4">
         <v>8.0194268946312501</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>0.43101363651047198</v>
       </c>
@@ -481,7 +3495,7 @@
         <v>7.6706379451610998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>0.44659010988831999</v>
       </c>
@@ -489,7 +3503,7 @@
         <v>7.3960385663382899</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>0.45028686684686697</v>
       </c>
@@ -497,7 +3511,7 @@
         <v>7.1467197652483696</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>0.46043614760323898</v>
       </c>
@@ -505,7 +3519,7 @@
         <v>6.9108258226786798</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>0.47429971254903103</v>
       </c>
@@ -513,7 +3527,7 @@
         <v>6.6512785579543001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>0.48325857893681101</v>
       </c>
@@ -521,7 +3535,7 @@
         <v>6.3540138335778602</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>0.51591922717260696</v>
       </c>
@@ -529,7 +3543,7 @@
         <v>6.0032094948647998</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>0.53718695454763898</v>
       </c>
@@ -537,7 +3551,7 @@
         <v>5.7398493876695502</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>0.55858156463269903</v>
       </c>
@@ -545,7 +3559,7 @@
         <v>5.4632851254104597</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>0.59375366235973304</v>
       </c>
@@ -553,7 +3567,7 @@
         <v>5.1841333053867098</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>0.62669473348914395</v>
       </c>
@@ -561,7 +3575,7 @@
         <v>4.94360459023265</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>0.65252401381103997</v>
       </c>
@@ -569,7 +3583,7 @@
         <v>4.7666841333053798</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>0.70012194249306403</v>
       </c>
@@ -577,7 +3591,7 @@
         <v>4.5461328861873804</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>0.76191418443192804</v>
       </c>
@@ -585,7 +3599,7 @@
         <v>4.3227048836721798</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>0.85204904417020899</v>
       </c>
@@ -593,7 +3607,7 @@
         <v>4.1277538537756504</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>0.97752558574144799</v>
       </c>
@@ -601,7 +3615,7 @@
         <v>4.0328223093890596</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>1.0791978159325599</v>
       </c>
@@ -609,7 +3623,7 @@
         <v>4.0521445856595699</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>1.1862839107121701</v>
       </c>
@@ -617,7 +3631,7 @@
         <v>4.1493208388644298</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>1.2870081642962199</v>
       </c>
@@ -625,7 +3639,7 @@
         <v>4.2873992492521102</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>1.36100064059708</v>
       </c>
@@ -633,7 +3647,7 @@
         <v>4.4378515822657496</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>1.41981629603586</v>
       </c>
@@ -641,7 +3655,7 @@
         <v>4.5401150469270304</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>1.4949566169159401</v>
       </c>
@@ -649,7 +3663,7 @@
         <v>4.4199043463348602</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>1.5991944755019301</v>
       </c>
@@ -657,7 +3671,7 @@
         <v>4.2900144814313697</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>1.7033913246227499</v>
       </c>
@@ -665,7 +3679,7 @@
         <v>4.1906356586193096</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>1.80754716427839</v>
       </c>
@@ -673,7 +3687,7 @@
         <v>4.1217678778986597</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>1.91168074165294</v>
       </c>
@@ -681,7 +3695,7 @@
         <v>4.0694632343133703</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>2.0157686227662901</v>
       </c>
@@ -689,7 +3703,7 @@
         <v>4.05115660905851</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32">
         <v>2.11983892839456</v>
       </c>
@@ -697,7 +3711,7 @@
         <v>4.0459261446999797</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33">
         <v>2.2238909555183599</v>
       </c>
@@ -705,7 +3719,7 @@
         <v>4.0542948876736302</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34">
         <v>2.3428187875559701</v>
       </c>
@@ -713,7 +3727,7 @@
         <v>4.1061758858761497</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35">
         <v>2.4505284834891699</v>
       </c>
@@ -721,7 +3735,7 @@
         <v>4.1710168124336997</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36">
         <v>2.5472019608643901</v>
       </c>
@@ -729,7 +3743,7 @@
         <v>4.1134710127898098</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37">
         <v>2.6401296844141999</v>
       </c>
@@ -737,7 +3751,7 @@
         <v>4.0649882814732896</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38">
         <v>2.7442220960970398</v>
       </c>
@@ -745,7 +3759,7 @@
         <v>4.0433109125207203</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39">
         <v>2.8483052904143702</v>
       </c>
@@ -753,7 +3767,7 @@
         <v>4.02849126350488</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40">
         <v>2.9523826262366701</v>
       </c>
@@ -761,7 +3775,7 @@
         <v>4.0180303347878201</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41">
         <v>3.05644472997191</v>
       </c>
@@ -769,7 +3783,7 @@
         <v>4.0189020788475798</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42">
         <v>3.1605033186101301</v>
       </c>
@@ -777,7 +3791,7 @@
         <v>4.0223890550865997</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43">
         <v>3.2645443317632798</v>
       </c>
@@ -785,7 +3799,7 @@
         <v>4.0389521922219398</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44">
         <v>3.36855466902546</v>
       </c>
@@ -793,7 +3807,7 @@
         <v>4.07833819223465</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45">
         <v>3.46137753873646</v>
       </c>
@@ -801,7 +3815,7 @@
         <v>4.1078667169947698</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46">
         <v>3.5766799104651699</v>
       </c>
@@ -809,7 +3823,7 @@
         <v>4.0793124072415603</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47">
         <v>3.6807822014131801</v>
       </c>
@@ -817,7 +3831,7 @@
         <v>4.0502848649987602</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>3.78485836553648</v>
       </c>
@@ -825,7 +3839,7 @@
         <v>4.0406956803414502</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>3.8889228126697302</v>
       </c>
@@ -833,7 +3847,7 @@
         <v>4.0398239362817003</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>3.99300249189004</v>
       </c>
@@ -841,7 +3855,7 @@
         <v>4.0276195194451301</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>4.0970540503342399</v>
       </c>
@@ -849,7 +3863,7 @@
         <v>4.0363369600426804</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52">
         <v>4.20111263897246</v>
       </c>
@@ -857,7 +3871,7 @@
         <v>4.0398239362817003</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53">
         <v>4.3051759144066999</v>
       </c>
@@ -865,7 +3879,7 @@
         <v>4.0398239362817003</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54">
       <c r="A54">
         <v>4.40923333134592</v>
       </c>
@@ -873,7 +3887,7 @@
         <v>4.0441826565804702</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55">
       <c r="A55">
         <v>4.5057817391363102</v>
       </c>
@@ -881,7 +3895,7 @@
         <v>4.0796886280537503</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56">
       <c r="A56">
         <v>4.6173411350303297</v>
       </c>
@@ -889,7 +3903,7 @@
         <v>4.0581305615365499</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57">
       <c r="A57">
         <v>4.7214290161436798</v>
       </c>
@@ -897,7 +3911,7 @@
         <v>4.0398239362817003</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58">
       <c r="A58">
         <v>4.8255086953639896</v>
       </c>
@@ -905,7 +3919,7 @@
         <v>4.0276195194451301</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59">
       <c r="A59">
         <v>4.92485506211362</v>
       </c>
@@ -914,16 +3928,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA55AFF-871B-8040-AC68-18094EB37EF8}">
-  <dimension ref="A1:E64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -931,7 +3948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
         <v>0.69365949999999998</v>
       </c>
@@ -945,7 +3962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
         <v>0.70164243999999998</v>
       </c>
@@ -956,18 +3973,21 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>0.70897235999999997</v>
       </c>
       <c r="B4">
         <v>14.384499</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>0.72100017000000005</v>
       </c>
@@ -975,7 +3995,7 @@
         <v>14.200761999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>0.72917756</v>
       </c>
@@ -983,7 +4003,7 @@
         <v>13.961719</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>0.74076512999999999</v>
       </c>
@@ -991,7 +4011,7 @@
         <v>13.722982999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>0.75618788999999997</v>
       </c>
@@ -999,7 +4019,7 @@
         <v>13.434774000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>0.76892545000000001</v>
       </c>
@@ -1007,7 +4027,7 @@
         <v>13.183244999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>0.77872666999999995</v>
       </c>
@@ -1015,7 +4035,7 @@
         <v>12.929596999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>0.78854221999999996</v>
       </c>
@@ -1023,7 +4043,7 @@
         <v>12.665296</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>0.79830619999999997</v>
       </c>
@@ -1031,7 +4051,7 @@
         <v>12.439349999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>0.80804279999999995</v>
       </c>
@@ -1039,7 +4059,7 @@
         <v>12.233782</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>0.82469415999999995</v>
       </c>
@@ -1047,7 +4067,7 @@
         <v>11.936441</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>0.83989459</v>
       </c>
@@ -1055,7 +4075,7 @@
         <v>11.687764</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>0.84596519000000003</v>
       </c>
@@ -1063,7 +4083,7 @@
         <v>11.469524</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>0.86626040000000004</v>
       </c>
@@ -1071,7 +4091,7 @@
         <v>11.150660999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>0.89029835000000002</v>
       </c>
@@ -1079,7 +4099,7 @@
         <v>10.862574</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>0.91906922000000002</v>
       </c>
@@ -1087,7 +4107,7 @@
         <v>10.572438</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>0.97988640000000005</v>
       </c>
@@ -1095,7 +4115,7 @@
         <v>10.370604</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>1.0654741999999999</v>
       </c>
@@ -1103,7 +4123,7 @@
         <v>10.344758000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>1.1206524</v>
       </c>
@@ -1111,7 +4131,7 @@
         <v>10.451408000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>1.1465675</v>
       </c>
@@ -1119,7 +4139,7 @@
         <v>10.236757000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>1.1776070000000001</v>
       </c>
@@ -1127,7 +4147,7 @@
         <v>9.9852959999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>1.2135119999999999</v>
       </c>
@@ -1135,7 +4155,7 @@
         <v>9.6993074000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>1.2421888000000001</v>
       </c>
@@ -1143,7 +4163,7 @@
         <v>9.4791290999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>1.2850618</v>
       </c>
@@ -1151,7 +4171,7 @@
         <v>9.2547422000000008</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>1.3279064</v>
       </c>
@@ -1159,7 +4179,7 @@
         <v>9.0514057999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>1.3849579999999999</v>
       </c>
@@ -1167,7 +4187,7 @@
         <v>8.8357861</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>1.4656572000000001</v>
       </c>
@@ -1175,7 +4195,7 @@
         <v>8.6224953000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>1.5661890000000001</v>
       </c>
@@ -1183,7 +4203,7 @@
         <v>8.4345473000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32">
         <v>1.6684581999999999</v>
       </c>
@@ -1191,7 +4211,7 @@
         <v>8.3616694999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33">
         <v>1.7734226</v>
       </c>
@@ -1199,7 +4219,7 @@
         <v>8.3950572999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34">
         <v>1.8539190999999999</v>
       </c>
@@ -1207,7 +4227,7 @@
         <v>8.3325823000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35">
         <v>1.9231365</v>
       </c>
@@ -1215,7 +4235,7 @@
         <v>8.1404008999999995</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36">
         <v>2.0199609999999999</v>
       </c>
@@ -1223,7 +4243,7 @@
         <v>7.9705178999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37">
         <v>2.1241660000000002</v>
       </c>
@@ -1231,7 +4251,7 @@
         <v>7.8650368999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38">
         <v>2.2283100999999998</v>
       </c>
@@ -1239,7 +4259,7 @@
         <v>7.8048865000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39">
         <v>2.3323874999999998</v>
       </c>
@@ -1247,7 +4267,7 @@
         <v>7.7944256000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40">
         <v>2.4346082999999998</v>
       </c>
@@ -1255,7 +4275,7 @@
         <v>7.7575507999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41">
         <v>2.5406909</v>
       </c>
@@ -1263,7 +4283,7 @@
         <v>7.6627922000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42">
         <v>2.6448456</v>
       </c>
@@ -1271,7 +4291,7 @@
         <v>7.5947962000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43">
         <v>2.7542341000000001</v>
       </c>
@@ -1279,7 +4299,7 @@
         <v>7.5430726999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44">
         <v>2.8530647</v>
       </c>
@@ -1287,7 +4307,7 @@
         <v>7.5259283999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45">
         <v>2.9571502999999999</v>
       </c>
@@ -1295,7 +4315,7 @@
         <v>7.5093652999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46">
         <v>3.0612111999999998</v>
       </c>
@@ -1303,7 +4323,7 @@
         <v>7.5111087999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47">
         <v>3.1653541999999999</v>
       </c>
@@ -1311,7 +4331,7 @@
         <v>7.4518301999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>3.2732804</v>
       </c>
@@ -1319,7 +4339,7 @@
         <v>7.3931617999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>3.3717191</v>
       </c>
@@ -1327,7 +4347,7 @@
         <v>7.3548051000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>3.4776997999999999</v>
       </c>
@@ -1335,7 +4355,7 @@
         <v>7.3358882000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>3.5849186999999998</v>
       </c>
@@ -1343,7 +4363,7 @@
         <v>7.3342416000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52">
         <v>3.6858018000000001</v>
       </c>
@@ -1351,7 +4371,7 @@
         <v>7.3541949000000004</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53">
         <v>3.7899072</v>
       </c>
@@ -1359,7 +4379,7 @@
         <v>7.3228121000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54">
       <c r="A54">
         <v>3.8940293000000001</v>
       </c>
@@ -1367,7 +4387,7 @@
         <v>7.2790505000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55">
       <c r="A55">
         <v>3.9981333999999999</v>
       </c>
@@ -1375,7 +4395,7 @@
         <v>7.2487138</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56">
       <c r="A56">
         <v>4.1116650999999997</v>
       </c>
@@ -1383,7 +4403,7 @@
         <v>7.2426116</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57">
       <c r="A57">
         <v>4.2146701000000002</v>
       </c>
@@ -1391,7 +4411,7 @@
         <v>7.2479389000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58">
       <c r="A58">
         <v>4.3197447999999996</v>
       </c>
@@ -1399,7 +4419,7 @@
         <v>7.2774814000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59">
       <c r="A59">
         <v>4.4247572000000002</v>
       </c>
@@ -1407,7 +4427,7 @@
         <v>7.2752147999999996</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60">
       <c r="A60">
         <v>4.5205415999999996</v>
       </c>
@@ -1415,7 +4435,7 @@
         <v>7.2564627000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61">
       <c r="A61">
         <v>4.6319990999999998</v>
       </c>
@@ -1423,7 +4443,7 @@
         <v>7.2295354999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62">
       <c r="A62">
         <v>4.7389124999999996</v>
       </c>
@@ -1431,7 +4451,7 @@
         <v>7.2205564999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63">
       <c r="A63">
         <v>4.8401315</v>
       </c>
@@ -1439,7 +4459,7 @@
         <v>7.2251766999999996</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64">
       <c r="A64">
         <v>4.9441525999999998</v>
       </c>
@@ -1448,16 +4468,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB0B3FE-F500-CA4D-A013-CE8D6B910F32}">
-  <dimension ref="A1:E59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1465,7 +4488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
         <v>0.4000049</v>
       </c>
@@ -1479,7 +4502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
         <v>0.40648326000000001</v>
       </c>
@@ -1490,18 +4513,21 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>0.41543380000000002</v>
       </c>
       <c r="B4">
         <v>9.0545801000000008</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>0.43714201000000003</v>
       </c>
@@ -1509,7 +4535,7 @@
         <v>8.7630300999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>0.44577772999999998</v>
       </c>
@@ -1517,7 +4543,7 @@
         <v>8.4786575000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>0.45675144000000001</v>
       </c>
@@ -1525,7 +4551,7 @@
         <v>8.2505415000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>0.46745274999999997</v>
       </c>
@@ -1533,7 +4559,7 @@
         <v>8.0250891000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>0.49328487999999998</v>
       </c>
@@ -1541,7 +4567,7 @@
         <v>7.7977569000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>0.50827582999999998</v>
       </c>
@@ -1549,7 +4575,7 @@
         <v>7.5285742999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>0.54785055000000005</v>
       </c>
@@ -1557,7 +4583,7 @@
         <v>7.2316525</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>0.63054036000000002</v>
       </c>
@@ -1565,7 +4591,7 @@
         <v>7.0455975000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>0.73671927999999998</v>
       </c>
@@ -1573,7 +4599,7 @@
         <v>7.0958233000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>0.81227959999999999</v>
       </c>
@@ -1581,7 +4607,7 @@
         <v>7.3219887999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>0.85038177999999998</v>
       </c>
@@ -1589,7 +4615,7 @@
         <v>7.5519558</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>0.89973572999999996</v>
       </c>
@@ -1597,7 +4623,7 @@
         <v>7.8610287999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>0.929701</v>
       </c>
@@ -1605,7 +4631,7 @@
         <v>8.0747804999999993</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>0.96640967</v>
       </c>
@@ -1613,7 +4639,7 @@
         <v>7.9040255999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>1.0023472</v>
       </c>
@@ -1621,7 +4647,7 @@
         <v>7.6990568000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>1.0553235000000001</v>
       </c>
@@ -1629,7 +4655,7 @@
         <v>7.4684901999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>1.1411538999999999</v>
       </c>
@@ -1637,7 +4663,7 @@
         <v>7.2260485000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>1.2454413</v>
       </c>
@@ -1645,7 +4671,7 @@
         <v>7.0593015000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>1.3495499</v>
       </c>
@@ -1653,7 +4679,7 @@
         <v>7.0255473000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>1.4535335</v>
       </c>
@@ -1661,7 +4687,7 @@
         <v>7.0848259000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>1.5526507000000001</v>
       </c>
@@ -1669,7 +4695,7 @@
         <v>7.2454884000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>1.6175938999999999</v>
       </c>
@@ -1677,7 +4703,7 @@
         <v>7.3935816000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>1.6593756</v>
       </c>
@@ -1685,7 +4711,7 @@
         <v>7.3015720999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>1.7561764</v>
       </c>
@@ -1693,7 +4719,7 @@
         <v>7.1493349999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>1.860358</v>
       </c>
@@ -1701,7 +4727,7 @@
         <v>7.0612887999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>1.9644752000000001</v>
       </c>
@@ -1709,7 +4735,7 @@
         <v>7.0211886000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>2.0685220000000002</v>
       </c>
@@ -1717,7 +4743,7 @@
         <v>7.0333930000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32">
         <v>2.1725173</v>
       </c>
@@ -1725,7 +4751,7 @@
         <v>7.0839542</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33">
         <v>2.2764646000000002</v>
       </c>
@@ -1733,7 +4759,7 @@
         <v>7.1702569</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34">
         <v>2.3805806</v>
       </c>
@@ -1741,7 +4767,7 @@
         <v>7.1310283999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35">
         <v>2.4847283</v>
       </c>
@@ -1749,7 +4775,7 @@
         <v>7.0682628000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36">
         <v>2.5888501000000002</v>
       </c>
@@ -1757,7 +4783,7 @@
         <v>7.0246756000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37">
         <v>2.6929297999999999</v>
       </c>
@@ -1765,7 +4791,7 @@
         <v>7.0124712000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38">
         <v>2.7969814</v>
       </c>
@@ -1773,7 +4799,7 @@
         <v>7.0211886000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39">
         <v>2.9009906999999999</v>
       </c>
@@ -1781,7 +4807,7 @@
         <v>7.0612887999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40">
         <v>3.0050411000000001</v>
       </c>
@@ -1789,7 +4815,7 @@
         <v>7.0708780000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41">
         <v>3.1091513000000002</v>
       </c>
@@ -1797,7 +4823,7 @@
         <v>7.0360082999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42">
         <v>3.2132472999999999</v>
       </c>
@@ -1805,7 +4831,7 @@
         <v>7.0115993999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43">
         <v>3.3173341000000001</v>
       </c>
@@ -1813,7 +4839,7 @@
         <v>6.9941646000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44">
         <v>3.421395</v>
       </c>
@@ -1821,7 +4847,7 @@
         <v>6.995908</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45">
         <v>3.525436</v>
       </c>
@@ -1829,7 +4855,7 @@
         <v>7.0124712000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46">
         <v>3.6294746999999998</v>
       </c>
@@ -1837,7 +4863,7 @@
         <v>7.0307778000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47">
         <v>3.7335180000000001</v>
       </c>
@@ -1845,7 +4871,7 @@
         <v>7.0455975000000004</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>3.8376210999999998</v>
       </c>
@@ -1853,7 +4879,7 @@
         <v>7.0159582</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>3.9417102000000002</v>
       </c>
@@ -1861,7 +4887,7 @@
         <v>6.9967797999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>4.0457817</v>
       </c>
@@ -1869,7 +4895,7 @@
         <v>6.9906775999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>4.1498378999999996</v>
       </c>
@@ -1877,7 +4903,7 @@
         <v>6.995908</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52">
         <v>4.2538707000000002</v>
       </c>
@@ -1885,7 +4911,7 @@
         <v>7.0185734000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53">
         <v>4.3579188000000002</v>
       </c>
@@ -1893,7 +4919,7 @@
         <v>7.0299060999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54">
       <c r="A54">
         <v>4.4620090000000001</v>
       </c>
@@ -1901,7 +4927,7 @@
         <v>7.0098558999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55">
       <c r="A55">
         <v>4.5660945000000002</v>
       </c>
@@ -1909,7 +4935,7 @@
         <v>6.9932927999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56">
       <c r="A56">
         <v>4.6701578000000001</v>
       </c>
@@ -1917,7 +4943,7 @@
         <v>6.9932927999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57">
       <c r="A57">
         <v>4.7742211000000001</v>
       </c>
@@ -1925,7 +4951,7 @@
         <v>6.9932927999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58">
       <c r="A58">
         <v>4.8782737999999997</v>
       </c>
@@ -1933,7 +4959,7 @@
         <v>7.0011384999999997</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59">
       <c r="A59">
         <v>4.9681281000000004</v>
       </c>
@@ -1942,16 +4968,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10A6864-76A2-644B-B374-E2A80CF26B2B}">
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1959,7 +4988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
         <v>0.68063501000000004</v>
       </c>
@@ -1973,7 +5002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
         <v>0.69613619000000004</v>
       </c>
@@ -1984,18 +5013,21 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>0.70279407000000005</v>
       </c>
       <c r="B4">
         <v>9.9905451999999997</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>0.72640420000000006</v>
       </c>
@@ -2003,7 +5035,7 @@
         <v>9.6267493000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>0.73623291000000002</v>
       </c>
@@ -2011,7 +5043,7 @@
         <v>9.3526507999999993</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>0.74836343000000005</v>
       </c>
@@ -2019,7 +5051,7 @@
         <v>9.1256211999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>0.76239595999999998</v>
       </c>
@@ -2027,7 +5059,7 @@
         <v>8.8911841999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>0.77405953999999999</v>
       </c>
@@ -2035,7 +5067,7 @@
         <v>8.6596373999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>0.80284672999999995</v>
       </c>
@@ -2043,7 +5075,7 @@
         <v>8.3573543000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>0.82866519999999999</v>
       </c>
@@ -2051,7 +5083,7 @@
         <v>7.9898303999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>0.86596698999999999</v>
       </c>
@@ -2059,7 +5091,7 @@
         <v>7.7279267999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>0.88706839999999998</v>
       </c>
@@ -2067,7 +5099,7 @@
         <v>7.4844644999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>0.92206856000000004</v>
       </c>
@@ -2075,7 +5107,7 @@
         <v>7.1678515000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>0.96656321000000001</v>
       </c>
@@ -2083,7 +5115,7 @@
         <v>6.9099868000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>1.0046712</v>
       </c>
@@ -2091,7 +5123,7 @@
         <v>6.7114773000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>1.0353209999999999</v>
       </c>
@@ -2099,7 +5131,7 @@
         <v>6.5316777000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>1.0833128000000001</v>
       </c>
@@ -2107,7 +5139,7 @@
         <v>6.3204959000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>1.1348597</v>
       </c>
@@ -2115,7 +5147,7 @@
         <v>6.1186502000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>1.187157</v>
       </c>
@@ -2123,7 +5155,7 @@
         <v>5.9676722</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>1.2945617</v>
       </c>
@@ -2131,7 +5163,7 @@
         <v>5.7060174000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>1.3987965</v>
       </c>
@@ -2139,7 +5171,7 @@
         <v>5.5784383999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>1.5029030999999999</v>
       </c>
@@ -2147,7 +5179,7 @@
         <v>5.5461976999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>1.6069617</v>
       </c>
@@ -2155,7 +5187,7 @@
         <v>5.5496846</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>1.7023615000000001</v>
       </c>
@@ -2163,7 +5195,7 @@
         <v>5.4276032000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>1.7966222000000001</v>
       </c>
@@ -2171,7 +5203,7 @@
         <v>5.2114479999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>1.9009503000000001</v>
       </c>
@@ -2179,7 +5211,7 @@
         <v>5.0144337999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>2.0014907000000002</v>
       </c>
@@ -2187,7 +5219,7 @@
         <v>4.8576788999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>2.1094624</v>
       </c>
@@ -2195,7 +5227,7 @@
         <v>4.7276300000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>2.2243051</v>
       </c>
@@ -2203,7 +5235,7 @@
         <v>4.6259627999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>2.3035931000000001</v>
       </c>
@@ -2211,7 +5243,7 @@
         <v>4.5828115</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32">
         <v>2.4218959</v>
       </c>
@@ -2219,7 +5251,7 @@
         <v>4.5463072000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33">
         <v>2.5286561000000001</v>
       </c>
@@ -2227,7 +5259,7 @@
         <v>4.5507904999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34">
         <v>2.6299790999999999</v>
       </c>
@@ -2235,7 +5267,7 @@
         <v>4.5785618000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35">
         <v>2.7349727000000001</v>
       </c>
@@ -2243,7 +5275,7 @@
         <v>4.5902431000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36">
         <v>2.8392179</v>
       </c>
@@ -2251,7 +5283,7 @@
         <v>4.5331342000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37">
         <v>2.9370501999999998</v>
       </c>
@@ -2259,7 +5291,7 @@
         <v>4.4766646000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38">
         <v>3.0432895000000002</v>
       </c>
@@ -2267,7 +5299,7 @@
         <v>4.4217931000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39">
         <v>3.1537076000000002</v>
       </c>
@@ -2275,7 +5307,7 @@
         <v>4.3860999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40">
         <v>3.2546469999999998</v>
       </c>
@@ -2283,7 +5315,7 @@
         <v>4.3641126999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41">
         <v>3.3618828000000001</v>
       </c>
@@ -2291,7 +5323,7 @@
         <v>4.3498742000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42">
         <v>3.4627970000000001</v>
       </c>
@@ -2299,7 +5331,7 @@
         <v>4.3466778000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43">
         <v>3.5763064999999998</v>
       </c>
@@ -2307,7 +5339,7 @@
         <v>4.3571388000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44">
         <v>3.6772117999999998</v>
       </c>
@@ -2315,7 +5347,7 @@
         <v>4.3605289000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45">
         <v>3.7844693999999999</v>
       </c>
@@ -2323,7 +5355,7 @@
         <v>4.3301147000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46">
         <v>3.8896331000000002</v>
       </c>
@@ -2331,7 +5363,7 @@
         <v>4.2934045999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47">
         <v>3.9926791000000001</v>
       </c>
@@ -2339,7 +5371,7 @@
         <v>4.2682209000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>4.1041280999999996</v>
       </c>
@@ -2347,7 +5379,7 @@
         <v>4.2475896000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>4.2008489999999998</v>
       </c>
@@ -2355,7 +5387,7 @@
         <v>4.2359663000000003</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>4.3049263</v>
       </c>
@@ -2363,7 +5395,7 @@
         <v>4.2255054000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>4.4089942999999998</v>
       </c>
@@ -2371,7 +5403,7 @@
         <v>4.2220183999999996</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52">
         <v>4.5319476999999999</v>
       </c>
@@ -2379,7 +5411,7 @@
         <v>4.2446837999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53">
         <v>4.6360016000000002</v>
       </c>
@@ -2387,7 +5419,7 @@
         <v>4.2516577</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54">
       <c r="A54">
         <v>4.7432366999999998</v>
       </c>
@@ -2395,7 +5427,7 @@
         <v>4.2380003999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55">
       <c r="A55">
         <v>4.8368070999999997</v>
       </c>
@@ -2403,7 +5435,7 @@
         <v>4.2241493999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56">
       <c r="A56">
         <v>4.9676457000000003</v>
       </c>
@@ -2412,16 +5444,18 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AAF5005-D9B0-9141-8B9E-B40FA37475A3}">
-  <dimension ref="A1:E58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2429,7 +5463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
         <v>0.47390399</v>
       </c>
@@ -2443,7 +5477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
         <v>0.49040493000000002</v>
       </c>
@@ -2454,18 +5488,21 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>0.50812086000000001</v>
       </c>
       <c r="B4">
         <v>5.4526304999999997</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>0.52330717000000004</v>
       </c>
@@ -2473,7 +5510,7 @@
         <v>5.1809368999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>0.54107190000000005</v>
       </c>
@@ -2481,7 +5518,7 @@
         <v>4.8964578000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>0.56299231000000005</v>
       </c>
@@ -2489,7 +5526,7 @@
         <v>4.5128903999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>0.57753504</v>
       </c>
@@ -2497,7 +5534,7 @@
         <v>4.2507859999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>0.58809537000000001</v>
       </c>
@@ -2505,7 +5542,7 @@
         <v>3.9737814999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>0.61349633999999997</v>
       </c>
@@ -2513,7 +5550,7 @@
         <v>3.6131052000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>0.64411156999999997</v>
       </c>
@@ -2521,7 +5558,7 @@
         <v>3.2832373000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>0.66428513</v>
       </c>
@@ -2529,7 +5566,7 @@
         <v>3.0548777</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>0.67609827</v>
       </c>
@@ -2537,7 +5574,7 @@
         <v>2.8248742</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>0.70200804000000006</v>
       </c>
@@ -2545,7 +5582,7 @@
         <v>2.5894598000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>0.72979181999999998</v>
       </c>
@@ -2553,7 +5590,7 @@
         <v>2.3674700999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>0.76669007</v>
       </c>
@@ -2561,7 +5598,7 @@
         <v>2.1356055999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>0.80675469</v>
       </c>
@@ -2569,7 +5606,7 @@
         <v>1.9306029</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>0.87830803000000002</v>
       </c>
@@ -2577,7 +5614,7 @@
         <v>1.671411</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>0.97393054000000001</v>
       </c>
@@ -2585,7 +5622,7 @@
         <v>1.4286890000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>1.0479404999999999</v>
       </c>
@@ -2593,7 +5630,7 @@
         <v>1.2652629</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>1.1493675000000001</v>
       </c>
@@ -2601,7 +5638,7 @@
         <v>1.1151226000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>1.2535795999999999</v>
       </c>
@@ -2609,7 +5646,7 @@
         <v>1.0044111</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>1.3577565</v>
       </c>
@@ -2617,7 +5654,7 @@
         <v>0.91985194999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>1.4619169999999999</v>
       </c>
@@ -2625,7 +5662,7 @@
         <v>0.84749719000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>1.5660588</v>
       </c>
@@ -2633,7 +5670,7 @@
         <v>0.78909034</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>1.6701900999999999</v>
       </c>
@@ -2641,7 +5678,7 @@
         <v>0.73852918000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>1.7743096</v>
       </c>
@@ -2649,7 +5686,7 @@
         <v>0.69668547000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>1.8784162</v>
       </c>
@@ -2657,7 +5694,7 @@
         <v>0.66443094000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>1.9825146</v>
       </c>
@@ -2665,7 +5702,7 @@
         <v>0.63827862000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>2.0866025000000001</v>
       </c>
@@ -2673,7 +5710,7 @@
         <v>0.61997199000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>2.1906916000000001</v>
       </c>
@@ -2681,7 +5718,7 @@
         <v>0.60079362000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32">
         <v>2.2947771000000001</v>
       </c>
@@ -2689,7 +5726,7 @@
         <v>0.58423048</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33">
         <v>2.3988615000000002</v>
       </c>
@@ -2697,7 +5734,7 @@
         <v>0.56853909000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34">
         <v>2.5029447</v>
       </c>
@@ -2705,7 +5742,7 @@
         <v>0.55371943999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35">
         <v>2.6070324999999999</v>
       </c>
@@ -2713,7 +5750,7 @@
         <v>0.53541282000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36">
         <v>2.7111157000000001</v>
       </c>
@@ -2721,7 +5758,7 @@
         <v>0.52059317000000005</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37">
         <v>2.8151918999999999</v>
       </c>
@@ -2729,7 +5766,7 @@
         <v>0.51100398000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38">
         <v>2.9192551999999998</v>
       </c>
@@ -2737,7 +5774,7 @@
         <v>0.51100398000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39">
         <v>3.0233384000000001</v>
       </c>
@@ -2745,7 +5782,7 @@
         <v>0.49618433000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40">
         <v>3.1274099</v>
       </c>
@@ -2753,7 +5790,7 @@
         <v>0.49008212000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41">
         <v>3.2314965999999998</v>
       </c>
@@ -2761,7 +5798,7 @@
         <v>0.47264724000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42">
         <v>3.3355598</v>
       </c>
@@ -2769,7 +5806,7 @@
         <v>0.47264724000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43">
         <v>3.4396429999999998</v>
       </c>
@@ -2777,7 +5814,7 @@
         <v>0.45782759000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44">
         <v>3.5437121999999999</v>
       </c>
@@ -2785,7 +5822,7 @@
         <v>0.45346887000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45">
         <v>3.6477754</v>
       </c>
@@ -2793,7 +5830,7 @@
         <v>0.45346887000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46">
         <v>3.7518563</v>
       </c>
@@ -2801,7 +5838,7 @@
         <v>0.44039271000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47">
         <v>3.8559277999999999</v>
       </c>
@@ -2809,7 +5846,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>3.959991</v>
       </c>
@@ -2817,7 +5854,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>4.0640590000000003</v>
       </c>
@@ -2825,7 +5862,7 @@
         <v>0.43080352999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>4.1681176000000004</v>
       </c>
@@ -2833,7 +5870,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>4.2721809000000004</v>
       </c>
@@ -2841,7 +5878,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52">
         <v>4.3762441000000001</v>
       </c>
@@ -2849,7 +5886,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53">
         <v>4.4803074000000001</v>
       </c>
@@ -2857,7 +5894,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54">
       <c r="A54">
         <v>4.5843707</v>
       </c>
@@ -2865,7 +5902,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55">
       <c r="A55">
         <v>4.688434</v>
       </c>
@@ -2873,7 +5910,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56">
       <c r="A56">
         <v>4.7924971999999997</v>
       </c>
@@ -2881,7 +5918,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57">
       <c r="A57">
         <v>4.8965604999999996</v>
       </c>
@@ -2889,7 +5926,7 @@
         <v>0.43429051000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58">
       <c r="A58">
         <v>4.9817143000000002</v>
       </c>
@@ -2898,16 +5935,18 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB65198-E773-D34A-B6B8-83C146B2A6A7}">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2915,7 +5954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2">
         <v>0.74732061000000005</v>
       </c>
@@ -2929,7 +5968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3">
         <v>0.75614968000000005</v>
       </c>
@@ -2940,18 +5979,21 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>0.76746513999999999</v>
       </c>
       <c r="B4">
         <v>10.252625999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>0.77807550999999997</v>
       </c>
@@ -2959,7 +6001,7 @@
         <v>9.9700459000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>0.80105440000000006</v>
       </c>
@@ -2967,7 +6009,7 @@
         <v>9.6908452</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>0.82122793000000005</v>
       </c>
@@ -2975,7 +6017,7 @@
         <v>9.4625079000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>0.84140466000000003</v>
       </c>
@@ -2983,7 +6025,7 @@
         <v>9.2317920999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>0.86917922999999997</v>
       </c>
@@ -2991,7 +6033,7 @@
         <v>8.9790530999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>0.90101589999999998</v>
       </c>
@@ -2999,7 +6041,7 @@
         <v>8.7541068000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>0.95434322999999999</v>
       </c>
@@ -3007,7 +6049,7 @@
         <v>8.4604380999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>0.99794808000000002</v>
       </c>
@@ -3015,7 +6057,7 @@
         <v>8.1942544999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>1.0379845999999999</v>
       </c>
@@ -3023,7 +6065,7 @@
         <v>7.9686041999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>1.0890515000000001</v>
       </c>
@@ -3031,7 +6073,7 @@
         <v>7.7814325000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>1.1644201999999999</v>
       </c>
@@ -3039,7 +6081,7 @@
         <v>7.5120677000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>1.2546786999999999</v>
       </c>
@@ -3047,7 +6089,7 @@
         <v>7.2251292999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>1.3300938</v>
       </c>
@@ -3055,7 +6097,7 @@
         <v>7.0479358999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>1.3922498999999999</v>
       </c>
@@ -3063,7 +6105,7 @@
         <v>6.9298330000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>1.4971372999999999</v>
       </c>
@@ -3071,7 +6113,7 @@
         <v>6.7077482000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>1.5890409999999999</v>
       </c>
@@ -3079,7 +6121,7 @@
         <v>6.5653753999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>1.7004011000000001</v>
       </c>
@@ -3087,7 +6129,7 @@
         <v>6.4153264999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>1.8117156000000001</v>
       </c>
@@ -3095,7 +6137,7 @@
         <v>6.2992755999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>1.9017132999999999</v>
       </c>
@@ -3103,7 +6145,7 @@
         <v>6.2063803000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>1.9687854</v>
       </c>
@@ -3111,7 +6153,7 @@
         <v>6.1604951000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>2.0697961</v>
       </c>
@@ -3119,7 +6161,7 @@
         <v>6.0854998</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>2.1739480000000002</v>
       </c>
@@ -3127,7 +6169,7 @@
         <v>6.0195546999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>2.2770408999999998</v>
       </c>
@@ -3135,7 +6177,7 @@
         <v>5.9594598999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>2.3727561000000001</v>
       </c>
@@ -3143,7 +6185,7 @@
         <v>5.9139768000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>2.4958184000000001</v>
       </c>
@@ -3151,7 +6193,7 @@
         <v>5.8556667999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>2.5988867999999998</v>
       </c>
@@ -3159,7 +6201,7 @@
         <v>5.8138230999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>2.7040475000000002</v>
       </c>
@@ -3167,7 +6209,7 @@
         <v>5.7793846000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32">
         <v>2.8081315</v>
       </c>
@@ -3175,7 +6217,7 @@
         <v>5.7639560000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33">
         <v>2.9122417999999999</v>
       </c>
@@ -3183,7 +6225,7 @@
         <v>5.7289241999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34">
         <v>3.0163319999999998</v>
       </c>
@@ -3191,7 +6233,7 @@
         <v>5.7089116000000004</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35">
       <c r="A35">
         <v>3.1204174999999998</v>
       </c>
@@ -3199,7 +6241,7 @@
         <v>5.6923691999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36">
         <v>3.2245180000000002</v>
       </c>
@@ -3207,7 +6249,7 @@
         <v>5.6647242999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37">
         <v>3.3285798</v>
       </c>
@@ -3215,7 +6257,7 @@
         <v>5.6658115999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38">
         <v>3.4327288</v>
       </c>
@@ -3223,7 +6265,7 @@
         <v>5.6019892999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39">
         <v>3.5367522999999998</v>
       </c>
@@ -3231,7 +6273,7 @@
         <v>5.6316286</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40">
         <v>3.6408437</v>
       </c>
@@ -3239,7 +6281,7 @@
         <v>5.6107066999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41">
         <v>3.7449455999999999</v>
       </c>
@@ -3247,7 +6289,7 @@
         <v>5.5819391999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42">
         <v>3.8490416999999999</v>
       </c>
@@ -3255,7 +6297,7 @@
         <v>5.5575302999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43">
         <v>3.9531201999999999</v>
       </c>
@@ -3263,7 +6305,7 @@
         <v>5.5461976999999996</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44">
         <v>4.057194</v>
       </c>
@@ -3271,7 +6313,7 @@
         <v>5.5383519999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45">
         <v>4.1612456</v>
       </c>
@@ -3279,7 +6321,7 @@
         <v>5.5470693999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46">
         <v>4.2652925000000002</v>
       </c>
@@ -3287,7 +6329,7 @@
         <v>5.5592737999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47">
         <v>4.3693346000000002</v>
       </c>
@@ -3295,7 +6337,7 @@
         <v>5.5749652000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>4.4734166999999996</v>
       </c>
@@ -3303,7 +6345,7 @@
         <v>5.5610172999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>4.5774917000000004</v>
       </c>
@@ -3311,7 +6353,7 @@
         <v>5.5522999000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>4.6815759999999997</v>
       </c>
@@ -3319,7 +6361,7 @@
         <v>5.5366084999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>4.7856405000000004</v>
       </c>
@@ -3327,7 +6369,7 @@
         <v>5.5357367000000002</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52">
         <v>4.8896861999999999</v>
       </c>
@@ -3335,7 +6377,7 @@
         <v>5.5488128999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53">
         <v>4.9558999999999997</v>
       </c>
@@ -3344,16 +6386,18 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73427316-DD07-C846-9C52-ED7D7C147642}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3361,7 +6405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="D2" t="s">
         <v>2</v>
       </c>
@@ -3369,15 +6413,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="D3" t="s">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>